--- a/model/data/invoice/sale/1405-07-02-sale-zibavash-express.xlsx
+++ b/model/data/invoice/sale/1405-07-02-sale-zibavash-express.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,127 +421,247 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v xml:space="preserve">ریمل گلدن رز مدل Flash رنگ زرشکی تیره شماره 10 </v>
+        <v xml:space="preserve">رژ لب مایع گلدن رز شماره 16 </v>
       </c>
       <c r="B2">
-        <v>82230424</v>
+        <v>37203276</v>
       </c>
       <c r="C2">
-        <v>22344727</v>
+        <v>1761811</v>
       </c>
       <c r="D2">
-        <v>7704900</v>
+        <v>9411800</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="str">
-        <v>00221880</v>
+        <v>00221070</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v xml:space="preserve">مداد لب گلدن رز مدل DREAM شماره 510 </v>
+        <v xml:space="preserve">ژل لیفت ابرو کولمار مدل N </v>
       </c>
       <c r="B3">
-        <v>34359481</v>
+        <v>63117064</v>
       </c>
       <c r="C3">
-        <v>1051424</v>
+        <v>14926956</v>
       </c>
       <c r="D3">
-        <v>3176000</v>
+        <v>4242100</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>00221222</v>
+        <v>00230050</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v xml:space="preserve">مداد لب فلورمار مدل ضد آب شماره 205 </v>
+        <v xml:space="preserve">مداد لب گلدن رز مدل Dream شماره 539 </v>
       </c>
       <c r="B4">
-        <v>57178901</v>
+        <v>57918432</v>
       </c>
       <c r="C4">
-        <v>16417869</v>
+        <v>16651496</v>
       </c>
       <c r="D4">
-        <v>5990000</v>
+        <v>3074000</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>00207063</v>
+        <v>00221744</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v xml:space="preserve">مداد لب فلورمار مدل بادوام شماره 201 </v>
+        <v xml:space="preserve">مداد لب گلدن رز مدل Mood Defining شماره 09 </v>
       </c>
       <c r="B5">
-        <v>38144310</v>
+        <v>76376317</v>
       </c>
       <c r="C5">
-        <v>10437360</v>
+        <v>21200215</v>
       </c>
       <c r="D5">
-        <v>5990000</v>
+        <v>3200000</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>00207061</v>
+        <v>00221802</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v xml:space="preserve">پودر تثبیت کننده آرایش فلورمار مدل Invisible </v>
+        <v xml:space="preserve">رژ لب جامد براق گلدن رز مدل Silky Shine شماره 215 </v>
       </c>
       <c r="B6">
-        <v>34343986</v>
+        <v>81948608</v>
       </c>
       <c r="C6">
-        <v>6431103</v>
+        <v>22276872</v>
       </c>
       <c r="D6">
-        <v>10499700</v>
+        <v>7046500</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>00207011</v>
+        <v>00221866</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve">خط چشم آدور کوین مدل  3DMAX </v>
+        <v xml:space="preserve">اسپری تثبیت کننده آرایش گلدن رز مدل Fixing حجم 120 میلی لیتر </v>
       </c>
       <c r="B7">
-        <v>49174543</v>
+        <v>17438302</v>
       </c>
       <c r="C7">
-        <v>10829220</v>
+        <v>1417903</v>
       </c>
       <c r="D7">
-        <v>4886600</v>
+        <v>7474200</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>00201134</v>
+        <v>00221001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v xml:space="preserve">ژل ابرو گلدن رز مدل Max Hold حجم 7 میلی لیتر </v>
+      </c>
+      <c r="B8">
+        <v>76377226</v>
+      </c>
+      <c r="C8">
+        <v>21199009</v>
+      </c>
+      <c r="D8">
+        <v>6229200</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="str">
+        <v>00221780</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v xml:space="preserve">سایه چشم گلدن رز مدل Terracotta کد 120 </v>
+      </c>
+      <c r="B9">
+        <v>41019819</v>
+      </c>
+      <c r="C9">
+        <v>994911</v>
+      </c>
+      <c r="D9">
+        <v>9390000</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>00221423</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v xml:space="preserve">سایه چشم گلدن رز مدل Terracotta کد 113 </v>
+      </c>
+      <c r="B10">
+        <v>41019789</v>
+      </c>
+      <c r="C10">
+        <v>8417479</v>
+      </c>
+      <c r="D10">
+        <v>9390000</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="str">
+        <v>00221422</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v xml:space="preserve">رژ گونه استیکی گلدن رز مدل Creamy شماره 102 </v>
+      </c>
+      <c r="B11">
+        <v>41021186</v>
+      </c>
+      <c r="C11">
+        <v>515051</v>
+      </c>
+      <c r="D11">
+        <v>11990000</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="str">
+        <v>00221438</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v xml:space="preserve">رژ لب جامد گلدن رز شماره 16 </v>
+      </c>
+      <c r="B12">
+        <v>31044531</v>
+      </c>
+      <c r="C12">
+        <v>7147064</v>
+      </c>
+      <c r="D12">
+        <v>5381400</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="str">
+        <v>00221039</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v xml:space="preserve">پودر تثبیت کننده آرایش فلورمار مدل Invisible </v>
+      </c>
+      <c r="B13">
+        <v>34343986</v>
+      </c>
+      <c r="C13">
+        <v>6431103</v>
+      </c>
+      <c r="D13">
+        <v>10499700</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="str">
+        <v>00207011</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
   </ignoredErrors>
 </worksheet>
 </file>